--- a/analysis/AVGO/AVGO-Model.xlsx
+++ b/analysis/AVGO/AVGO-Model.xlsx
@@ -274,27 +274,27 @@
     </comment>
     <comment ref="F6" authorId="0" shapeId="0">
       <text>
-        <t>[E] BASE FY2026 AI ~$48B: Q1 $8.4B + Q2 guide $10.7B + H2 ramp; ties to ~$94B consensus total</t>
+        <t>[E] BASE FY2026 AI ~$50B: H1 actual $19.2B + Q3 guide implies ~$13B AI + Q4 continued ramp; mgmt reiterated FY26 AI guidance</t>
       </text>
     </comment>
     <comment ref="G6" authorId="0" shapeId="0">
       <text>
-        <t>[E] BASE FY2027 AI ~$76B: HAIRCUT ~24% vs mgmt 'line of sight to $100B+ AI in 2027' for execution / OpenAI-financing risk</t>
+        <t>[E] BASE FY2027 AI ~$85B: 15% haircut vs mgmt 'line of sight to $100B+ in FY27' (reiterated post-Q2). Q2 momentum reduces but does not eliminate execution / OpenAI-financing risk</t>
       </text>
     </comment>
     <comment ref="H6" authorId="0" shapeId="0">
       <text>
-        <t>[E] BASE FY2028 AI ~$98B (+29%): continued XPU + AI networking ramp across 6 committed customers</t>
+        <t>[E] BASE FY2028 AI ~$108B (+27%): continued XPU + AI networking ramp across 6 committed customers</t>
       </text>
     </comment>
     <comment ref="I6" authorId="0" shapeId="0">
       <text>
-        <t>[E] BASE FY2029 AI ~$116B (+18%): maturing hyperscaler programs, slowing growth</t>
+        <t>[E] BASE FY2029 AI ~$128B (+19%): maturing hyperscaler programs</t>
       </text>
     </comment>
     <comment ref="J6" authorId="0" shapeId="0">
       <text>
-        <t>[E] BASE FY2030 AI ~$131B (+13%): late-cycle AI accelerator demand</t>
+        <t>[E] BASE FY2030 AI ~$145B (+13%): late-cycle AI accelerator demand</t>
       </text>
     </comment>
     <comment ref="C7" authorId="0" shapeId="0">
@@ -579,22 +579,22 @@
     </comment>
     <comment ref="C22" authorId="0" shapeId="0">
       <text>
-        <t>AVGO ~$460/sh (close ~$459.97, June 1, 2026)</t>
+        <t>AVGO ~$481.62/sh post-Q2 FY26 print (+4.7% on $22.2B rev, AI +143%, Q3 guide $29.4B)</t>
       </text>
     </comment>
     <comment ref="C23" authorId="0" shapeId="0">
       <text>
-        <t>~4.73B diluted shares (StockAnalysis, Q1 FY26)</t>
+        <t>~4.73B diluted shares (StockAnalysis, Q2 FY26)</t>
       </text>
     </comment>
     <comment ref="C24" authorId="0" shapeId="0">
       <text>
-        <t>Total debt ~$66.1B at Feb 1, 2026 (Q1 FY26 8-K balance sheet)</t>
+        <t>[E] Total debt ~$65B at May 3, 2026 (Q2 FY26 8-K; continuing paydown from ~$66.1B in Q1)</t>
       </text>
     </comment>
     <comment ref="C25" authorId="0" shapeId="0">
       <text>
-        <t>Cash ~$14.2B at Feb 1, 2026 (Q1 FY26 8-K)</t>
+        <t>[E] Cash ~$16B at May 3, 2026 (Q2 FY26 — strong FCF $10.3B added)</t>
       </text>
     </comment>
     <comment ref="C26" authorId="0" shapeId="0">
@@ -1069,7 +1069,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>As of June 2026 | $ in millions unless noted | Blue = input/assumption (see cell comments), Black = formula</t>
+          <t>As of June 3, 2026 (post-Q2 FY26 print) | $ in millions unless noted | Blue = input/assumption (see cell comments), Black = formula</t>
         </is>
       </c>
     </row>
@@ -1143,19 +1143,19 @@
         <v>20000</v>
       </c>
       <c r="F6" s="6" t="n">
-        <v>48000</v>
+        <v>50000</v>
       </c>
       <c r="G6" s="6" t="n">
-        <v>76000</v>
+        <v>85000</v>
       </c>
       <c r="H6" s="6" t="n">
-        <v>98000</v>
+        <v>108000</v>
       </c>
       <c r="I6" s="6" t="n">
-        <v>116000</v>
+        <v>128000</v>
       </c>
       <c r="J6" s="6" t="n">
-        <v>131000</v>
+        <v>145000</v>
       </c>
     </row>
     <row r="7">
@@ -1561,7 +1561,7 @@
         </is>
       </c>
       <c r="C22" s="12" t="n">
-        <v>460</v>
+        <v>481.62</v>
       </c>
     </row>
     <row r="23">
@@ -1581,7 +1581,7 @@
         </is>
       </c>
       <c r="C24" s="6" t="n">
-        <v>66057</v>
+        <v>65000</v>
       </c>
     </row>
     <row r="25">
@@ -1591,7 +1591,7 @@
         </is>
       </c>
       <c r="C25" s="6" t="n">
-        <v>14200</v>
+        <v>16000</v>
       </c>
     </row>
     <row r="26">
